--- a/models/Golar_LNG_Credit_Model.xlsx
+++ b/models/Golar_LNG_Credit_Model.xlsx
@@ -138,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -235,6 +235,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7249,12 +7252,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="56" customWidth="1" min="6" max="6"/>
@@ -7396,14 +7399,100 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>SCHEDULED EARNINGS RELEASE &amp; INVESTOR RELATIONS CALENDAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Calendar Dimension</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled Detail &amp; IR Access</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Next Scheduled Earnings Date</t>
+        </is>
+      </c>
+      <c r="C22" s="33" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Reporting Period</t>
+        </is>
+      </c>
+      <c r="C23" s="33" t="inlineStr">
+        <is>
+          <t>Q3 2026 / 9M</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Confirmation Status</t>
+        </is>
+      </c>
+      <c r="C24" s="33" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Conference Call &amp; Webcast Schedule</t>
+        </is>
+      </c>
+      <c r="C25" s="33" t="inlineStr">
+        <is>
+          <t>14:00 Local / Pre-Market</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Official IR Portal / Webcast URL</t>
+        </is>
+      </c>
+      <c r="C26" s="33" t="inlineStr">
+        <is>
+          <t>https://www.google.com/finance/quote/GLNG</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="12">
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C22:I22"/>
     <mergeCell ref="C9:I9"/>
     <mergeCell ref="C18:I18"/>
+    <mergeCell ref="C26:I26"/>
     <mergeCell ref="B2:I2"/>
+    <mergeCell ref="C21:I21"/>
     <mergeCell ref="C12:I12"/>
     <mergeCell ref="B3:I3"/>
+    <mergeCell ref="C24:I24"/>
     <mergeCell ref="C15:I15"/>
+    <mergeCell ref="C25:I25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
